--- a/dataset_agreed/saved_models/baserun/pointcloud_base_run6/epoch_30/per_file_predictions_epoch_30.xlsx
+++ b/dataset_agreed/saved_models/baserun/pointcloud_base_run6/epoch_30/per_file_predictions_epoch_30.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="517">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="520">
   <si>
     <t>Filename</t>
   </si>
@@ -808,763 +808,772 @@
     <t>0,1,1,0</t>
   </si>
   <si>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
     <t>0,1,0,1</t>
   </si>
   <si>
-    <t>0.7188,0.0154,0.0215,0.1124</t>
-  </si>
-  <si>
-    <t>0.0002,0.0011,0.0000,0.9999</t>
-  </si>
-  <si>
-    <t>0.0922,0.0050,0.0003,0.9498</t>
-  </si>
-  <si>
-    <t>0.0036,0.0044,0.0003,0.9976</t>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
+    <t>0.8401,0.0329,0.0131,0.0249</t>
+  </si>
+  <si>
+    <t>0.0006,0.0003,0.0000,0.9998</t>
+  </si>
+  <si>
+    <t>0.2941,0.0003,0.0005,0.8675</t>
+  </si>
+  <si>
+    <t>0.0072,0.0039,0.0001,0.9966</t>
+  </si>
+  <si>
+    <t>0.9997,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9979,0.0012,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.9973,0.0019,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9968,0.0033,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9987,0.0009,0.0000,0.0001</t>
   </si>
   <si>
     <t>0.9997,0.0001,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9961,0.0025,0.0002,0.0004</t>
-  </si>
-  <si>
-    <t>0.9985,0.0008,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9998,0.0000,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9947,0.0038,0.0000,0.0003</t>
-  </si>
-  <si>
-    <t>0.9993,0.0004,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9995,0.0002,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9988,0.0005,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.5691,0.0013,0.4867,0.0006</t>
-  </si>
-  <si>
-    <t>0.0167,0.0036,0.9784,0.0001</t>
-  </si>
-  <si>
-    <t>0.4106,0.0003,0.7140,0.0001</t>
-  </si>
-  <si>
-    <t>0.0203,0.0012,0.9686,0.0010</t>
-  </si>
-  <si>
-    <t>0.1513,0.0006,0.8558,0.0018</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0009,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0006,0.0000</t>
-  </si>
-  <si>
-    <t>0.0013,0.9981,0.0013,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9997,0.0008,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0011,0.0000</t>
-  </si>
-  <si>
-    <t>0.6374,0.0008,0.3708,0.0021</t>
-  </si>
-  <si>
-    <t>0.6832,0.0005,0.2253,0.0058</t>
-  </si>
-  <si>
-    <t>0.0021,0.0000,0.9973,0.0002</t>
-  </si>
-  <si>
-    <t>0.1879,0.0015,0.7956,0.0020</t>
-  </si>
-  <si>
-    <t>0.0179,0.0000,0.9798,0.0002</t>
-  </si>
-  <si>
-    <t>0.2040,0.0002,0.7897,0.0018</t>
-  </si>
-  <si>
-    <t>0.0006,0.0000,0.9987,0.0005</t>
-  </si>
-  <si>
-    <t>0.0036,0.9949,0.0014,0.0005</t>
-  </si>
-  <si>
-    <t>0.2139,0.0370,0.6555,0.0022</t>
-  </si>
-  <si>
-    <t>0.0004,0.0109,0.9980,0.0161</t>
-  </si>
-  <si>
-    <t>0.0027,0.9929,0.0061,0.0003</t>
-  </si>
-  <si>
-    <t>0.2790,0.0013,0.7535,0.0030</t>
-  </si>
-  <si>
-    <t>0.7701,0.0084,0.2007,0.0031</t>
-  </si>
-  <si>
-    <t>0.1438,0.8611,0.0046,0.0006</t>
-  </si>
-  <si>
-    <t>0.0004,0.9990,0.0022,0.0000</t>
-  </si>
-  <si>
-    <t>0.0313,0.7409,0.1702,0.0030</t>
-  </si>
-  <si>
-    <t>0.4243,0.0001,0.5562,0.0012</t>
-  </si>
-  <si>
-    <t>0.0327,0.0082,0.9475,0.0013</t>
-  </si>
-  <si>
-    <t>0.0513,0.0001,0.7191,0.0426</t>
-  </si>
-  <si>
-    <t>0.0237,0.0395,0.9478,0.0005</t>
-  </si>
-  <si>
-    <t>0.0006,0.9970,0.0126,0.0000</t>
-  </si>
-  <si>
-    <t>0.0095,0.0023,0.9888,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.9962,0.0000,0.9441</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9997,0.0293,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0041,0.0000</t>
-  </si>
-  <si>
-    <t>0.0361,0.0485,0.9072,0.0015</t>
-  </si>
-  <si>
-    <t>0.0093,0.5265,0.8682,0.0012</t>
-  </si>
-  <si>
-    <t>0.0291,0.0000,0.9447,0.0035</t>
-  </si>
-  <si>
-    <t>0.0005,0.0000,0.9993,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.9999,0.0001</t>
-  </si>
-  <si>
-    <t>0.0046,0.0198,0.9847,0.0013</t>
-  </si>
-  <si>
-    <t>0.8348,0.2005,0.0012,0.0009</t>
-  </si>
-  <si>
-    <t>0.9600,0.0046,0.0150,0.0069</t>
-  </si>
-  <si>
-    <t>0.9934,0.0058,0.0002,0.0003</t>
-  </si>
-  <si>
-    <t>0.0018,0.0159,0.9966,0.0022</t>
-  </si>
-  <si>
-    <t>0.9968,0.0016,0.0002,0.0004</t>
-  </si>
-  <si>
-    <t>0.9942,0.0028,0.0002,0.0010</t>
-  </si>
-  <si>
-    <t>0.9283,0.0823,0.0017,0.0010</t>
-  </si>
-  <si>
-    <t>0.0000,0.9728,0.9788,0.0000</t>
-  </si>
-  <si>
-    <t>0.0382,0.0281,0.9347,0.0011</t>
-  </si>
-  <si>
-    <t>0.0379,0.0044,0.9274,0.0077</t>
-  </si>
-  <si>
-    <t>0.0001,0.9890,0.8999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0007,0.0002,0.9991,0.0000</t>
-  </si>
-  <si>
-    <t>0.0012,0.9980,0.0021,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.2758,0.0011,0.7985,0.0007</t>
-  </si>
-  <si>
-    <t>0.0340,0.0149,0.9480,0.0008</t>
-  </si>
-  <si>
-    <t>0.0139,0.0010,0.9861,0.0003</t>
-  </si>
-  <si>
-    <t>0.0000,0.9912,0.8549,0.0000</t>
-  </si>
-  <si>
-    <t>0.0006,0.9679,0.7961,0.0001</t>
-  </si>
-  <si>
-    <t>0.0005,0.9969,0.0142,0.0001</t>
-  </si>
-  <si>
-    <t>0.0013,0.9703,0.4552,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.0002,0.9999</t>
-  </si>
-  <si>
-    <t>0.0000,0.0002,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.0001,0.0000,0.9999</t>
-  </si>
-  <si>
-    <t>0.0001,0.0007,0.0000,0.9999</t>
+    <t>0.9971,0.0012,0.0002,0.0004</t>
+  </si>
+  <si>
+    <t>0.4752,0.0036,0.4667,0.0048</t>
+  </si>
+  <si>
+    <t>0.0371,0.0003,0.9699,0.0001</t>
+  </si>
+  <si>
+    <t>0.5131,0.0013,0.6080,0.0001</t>
+  </si>
+  <si>
+    <t>0.0011,0.0002,0.9978,0.0005</t>
+  </si>
+  <si>
+    <t>0.8694,0.0013,0.1714,0.0003</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0010,0.0000</t>
+  </si>
+  <si>
+    <t>0.0018,0.9974,0.0015,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9997,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0008,0.0000</t>
+  </si>
+  <si>
+    <t>0.4576,0.0004,0.6200,0.0005</t>
+  </si>
+  <si>
+    <t>0.1112,0.0029,0.8549,0.0037</t>
+  </si>
+  <si>
+    <t>0.0018,0.0000,0.9977,0.0001</t>
+  </si>
+  <si>
+    <t>0.3092,0.0017,0.6346,0.0063</t>
+  </si>
+  <si>
+    <t>0.0277,0.0000,0.9788,0.0000</t>
+  </si>
+  <si>
+    <t>0.5766,0.0003,0.3686,0.0047</t>
+  </si>
+  <si>
+    <t>0.0023,0.0000,0.9952,0.0013</t>
+  </si>
+  <si>
+    <t>0.0349,0.9559,0.0045,0.0020</t>
+  </si>
+  <si>
+    <t>0.1991,0.0252,0.7160,0.0018</t>
+  </si>
+  <si>
+    <t>0.0013,0.0042,0.9969,0.0030</t>
+  </si>
+  <si>
+    <t>0.0014,0.9950,0.0083,0.0002</t>
+  </si>
+  <si>
+    <t>0.8813,0.0075,0.0877,0.0020</t>
+  </si>
+  <si>
+    <t>0.8868,0.0209,0.0525,0.0021</t>
+  </si>
+  <si>
+    <t>0.2034,0.7784,0.0113,0.0009</t>
+  </si>
+  <si>
+    <t>0.0003,0.9994,0.0015,0.0000</t>
+  </si>
+  <si>
+    <t>0.0104,0.9413,0.1003,0.0030</t>
+  </si>
+  <si>
+    <t>0.1010,0.0010,0.8540,0.0047</t>
+  </si>
+  <si>
+    <t>0.0647,0.3237,0.6552,0.0063</t>
+  </si>
+  <si>
+    <t>0.0697,0.0000,0.9058,0.0013</t>
+  </si>
+  <si>
+    <t>0.0113,0.0130,0.9778,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.9998,0.0006,0.0000</t>
+  </si>
+  <si>
+    <t>0.0067,0.0025,0.9840,0.0036</t>
+  </si>
+  <si>
+    <t>0.0035,0.7466,0.0023,0.8845</t>
+  </si>
+  <si>
+    <t>0.0001,0.9999,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9998,0.0168,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0007,0.0000</t>
+  </si>
+  <si>
+    <t>0.0052,0.0418,0.9803,0.0003</t>
+  </si>
+  <si>
+    <t>0.0375,0.0280,0.9332,0.0005</t>
+  </si>
+  <si>
+    <t>0.0089,0.0000,0.9819,0.0029</t>
+  </si>
+  <si>
+    <t>0.0073,0.0000,0.9937,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0002,0.9995,0.0013</t>
+  </si>
+  <si>
+    <t>0.0090,0.0311,0.9726,0.0003</t>
+  </si>
+  <si>
+    <t>0.7634,0.3332,0.0006,0.0003</t>
+  </si>
+  <si>
+    <t>0.9889,0.0019,0.0036,0.0022</t>
+  </si>
+  <si>
+    <t>0.9942,0.0046,0.0003,0.0003</t>
+  </si>
+  <si>
+    <t>0.0044,0.0036,0.9943,0.0043</t>
+  </si>
+  <si>
+    <t>0.9964,0.0005,0.0001,0.0013</t>
+  </si>
+  <si>
+    <t>0.9971,0.0016,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.7418,0.3191,0.0017,0.0007</t>
+  </si>
+  <si>
+    <t>0.0008,0.8960,0.9182,0.0003</t>
+  </si>
+  <si>
+    <t>0.0232,0.0031,0.9647,0.0009</t>
+  </si>
+  <si>
+    <t>0.0054,0.0012,0.9886,0.0020</t>
+  </si>
+  <si>
+    <t>0.0000,0.9825,0.9851,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0000,0.9997,0.0000</t>
+  </si>
+  <si>
+    <t>0.0005,0.9989,0.0019,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.6003,0.0020,0.5218,0.0003</t>
+  </si>
+  <si>
+    <t>0.5792,0.0443,0.3358,0.0028</t>
+  </si>
+  <si>
+    <t>0.0042,0.0008,0.9954,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.9965,0.7083,0.0000</t>
+  </si>
+  <si>
+    <t>0.0005,0.9762,0.7511,0.0000</t>
+  </si>
+  <si>
+    <t>0.0022,0.9677,0.1893,0.0001</t>
+  </si>
+  <si>
+    <t>0.0005,0.9781,0.6395,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.0001,0.9999</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.0000,1.0000</t>
   </si>
   <si>
     <t>0.0001,0.0001,0.0000,1.0000</t>
   </si>
   <si>
-    <t>0.0000,0.0004,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9903,0.4370,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9870,0.9500,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9872,0.8805,0.0000</t>
-  </si>
-  <si>
-    <t>0.0010,0.9423,0.7558,0.0012</t>
-  </si>
-  <si>
-    <t>0.0001,0.9814,0.9262,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9946,0.3626,0.0001</t>
-  </si>
-  <si>
-    <t>0.9961,0.0041,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9745,0.0378,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9887,0.0049,0.0002,0.0014</t>
-  </si>
-  <si>
-    <t>0.9882,0.0114,0.0002,0.0003</t>
-  </si>
-  <si>
-    <t>0.9922,0.0063,0.0002,0.0004</t>
-  </si>
-  <si>
-    <t>0.9868,0.0048,0.0005,0.0031</t>
-  </si>
-  <si>
-    <t>0.9921,0.0075,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9991,0.0003,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.9994,0.0003,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9993,0.0002,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.9997,0.0000,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9971,0.0004,0.0000,0.0010</t>
-  </si>
-  <si>
-    <t>0.9955,0.0031,0.0001,0.0003</t>
-  </si>
-  <si>
-    <t>0.9980,0.0009,0.0001,0.0003</t>
-  </si>
-  <si>
-    <t>0.9994,0.0002,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.0004,0.0000,0.9993,0.0002</t>
-  </si>
-  <si>
-    <t>0.5501,0.0022,0.5151,0.0004</t>
-  </si>
-  <si>
-    <t>0.7715,0.0002,0.1942,0.0031</t>
-  </si>
-  <si>
-    <t>0.0013,0.0000,0.9983,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.9999,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0007,0.0000</t>
-  </si>
-  <si>
-    <t>0.0050,0.9936,0.0009,0.0001</t>
-  </si>
-  <si>
-    <t>0.0013,0.9980,0.0008,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0262,0.9808,0.0007,0.0000</t>
-  </si>
-  <si>
-    <t>0.5729,0.1137,0.1103,0.0064</t>
-  </si>
-  <si>
-    <t>0.0281,0.0013,0.9589,0.0022</t>
-  </si>
-  <si>
-    <t>0.6044,0.0095,0.3363,0.0047</t>
-  </si>
-  <si>
-    <t>0.8199,0.0042,0.1288,0.0027</t>
-  </si>
-  <si>
-    <t>0.0002,0.2626,0.0002,0.9954</t>
-  </si>
-  <si>
-    <t>0.0000,0.9998,0.0126,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0001,0.0028</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9997,0.9042,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9997,0.0018,0.0000</t>
-  </si>
-  <si>
-    <t>0.0177,0.9760,0.0069,0.0001</t>
-  </si>
-  <si>
-    <t>0.0208,0.9781,0.0028,0.0001</t>
-  </si>
-  <si>
-    <t>0.9242,0.0539,0.0011,0.0024</t>
-  </si>
-  <si>
-    <t>0.9921,0.0013,0.0007,0.0015</t>
-  </si>
-  <si>
-    <t>0.9955,0.0003,0.0002,0.0027</t>
-  </si>
-  <si>
-    <t>0.9977,0.0005,0.0003,0.0004</t>
-  </si>
-  <si>
-    <t>0.9876,0.0047,0.0005,0.0017</t>
-  </si>
-  <si>
-    <t>0.9669,0.0172,0.0046,0.0018</t>
-  </si>
-  <si>
-    <t>0.9921,0.0021,0.0005,0.0024</t>
-  </si>
-  <si>
-    <t>0.9922,0.0019,0.0009,0.0019</t>
-  </si>
-  <si>
-    <t>0.0001,0.8634,0.9918,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.5481,0.9974,0.0000</t>
-  </si>
-  <si>
-    <t>0.1693,0.0077,0.8024,0.0003</t>
-  </si>
-  <si>
-    <t>0.0714,0.0004,0.9384,0.0002</t>
-  </si>
-  <si>
-    <t>0.9456,0.0012,0.0193,0.0012</t>
-  </si>
-  <si>
-    <t>0.9142,0.0083,0.0306,0.0013</t>
-  </si>
-  <si>
-    <t>0.0441,0.0001,0.9575,0.0007</t>
-  </si>
-  <si>
-    <t>0.6694,0.0082,0.2000,0.0144</t>
-  </si>
-  <si>
-    <t>0.0010,0.0000,0.0000,0.9997</t>
+    <t>0.0014,0.0015,0.0001,0.9992</t>
+  </si>
+  <si>
+    <t>0.0004,0.0001,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.0000,0.0014,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.9924,0.1775,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9888,0.9605,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9802,0.9125,0.0000</t>
+  </si>
+  <si>
+    <t>0.0036,0.5803,0.8966,0.0008</t>
+  </si>
+  <si>
+    <t>0.0000,0.9883,0.9885,0.0000</t>
+  </si>
+  <si>
+    <t>0.0006,0.9500,0.7396,0.0001</t>
+  </si>
+  <si>
+    <t>0.9994,0.0003,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9993,0.0005,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9828,0.0240,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9954,0.0025,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.9962,0.0025,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9968,0.0019,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.9950,0.0029,0.0002,0.0006</t>
+  </si>
+  <si>
+    <t>0.9870,0.0140,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9990,0.0003,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.9965,0.0033,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9994,0.0002,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.9997,0.0000,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.9986,0.0003,0.0001,0.0005</t>
+  </si>
+  <si>
+    <t>0.9974,0.0010,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9992,0.0003,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9981,0.0001,0.0000,0.0010</t>
+  </si>
+  <si>
+    <t>0.0002,0.0000,0.9997,0.0001</t>
+  </si>
+  <si>
+    <t>0.2266,0.0002,0.8258,0.0002</t>
+  </si>
+  <si>
+    <t>0.9091,0.0009,0.0260,0.0073</t>
+  </si>
+  <si>
+    <t>0.0237,0.0001,0.9710,0.0009</t>
+  </si>
+  <si>
+    <t>0.0005,0.9993,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.0032,0.9955,0.0012,0.0000</t>
+  </si>
+  <si>
+    <t>0.0014,0.9975,0.0015,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9999,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.1073,0.9253,0.0013,0.0002</t>
+  </si>
+  <si>
+    <t>0.2761,0.3561,0.1325,0.0100</t>
+  </si>
+  <si>
+    <t>0.5935,0.0001,0.5356,0.0001</t>
+  </si>
+  <si>
+    <t>0.5058,0.0361,0.1350,0.0686</t>
+  </si>
+  <si>
+    <t>0.4433,0.2424,0.0419,0.0232</t>
+  </si>
+  <si>
+    <t>0.0000,0.3502,0.0000,0.9971</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0039,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0010,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0010,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9992,0.6097,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9998,0.0012,0.0000</t>
+  </si>
+  <si>
+    <t>0.0092,0.9794,0.0237,0.0001</t>
+  </si>
+  <si>
+    <t>0.0421,0.9457,0.0116,0.0007</t>
+  </si>
+  <si>
+    <t>0.8686,0.1194,0.0029,0.0030</t>
+  </si>
+  <si>
+    <t>0.9966,0.0006,0.0003,0.0006</t>
+  </si>
+  <si>
+    <t>0.9950,0.0007,0.0003,0.0022</t>
+  </si>
+  <si>
+    <t>0.9943,0.0011,0.0010,0.0014</t>
+  </si>
+  <si>
+    <t>0.9915,0.0023,0.0003,0.0014</t>
+  </si>
+  <si>
+    <t>0.9747,0.0124,0.0033,0.0011</t>
+  </si>
+  <si>
+    <t>0.9984,0.0002,0.0002,0.0007</t>
+  </si>
+  <si>
+    <t>0.9881,0.0017,0.0014,0.0053</t>
+  </si>
+  <si>
+    <t>0.0009,0.9215,0.8305,0.0002</t>
+  </si>
+  <si>
+    <t>0.0005,0.1144,0.9969,0.0000</t>
+  </si>
+  <si>
+    <t>0.0334,0.0021,0.9585,0.0001</t>
+  </si>
+  <si>
+    <t>0.0696,0.0094,0.9108,0.0002</t>
+  </si>
+  <si>
+    <t>0.9342,0.0021,0.0281,0.0010</t>
+  </si>
+  <si>
+    <t>0.7805,0.0012,0.2409,0.0010</t>
+  </si>
+  <si>
+    <t>0.0994,0.0004,0.8666,0.0065</t>
+  </si>
+  <si>
+    <t>0.6829,0.0508,0.0276,0.0386</t>
+  </si>
+  <si>
+    <t>0.0133,0.0011,0.0000,0.9951</t>
   </si>
   <si>
     <t>0.0000,0.0005,0.0000,1.0000</t>
   </si>
   <si>
-    <t>0.0000,0.0016,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0007,0.0000,0.0000,0.9998</t>
-  </si>
-  <si>
-    <t>0.0001,0.9921,0.8778,0.0000</t>
-  </si>
-  <si>
-    <t>0.9936,0.0041,0.0004,0.0002</t>
-  </si>
-  <si>
-    <t>0.0016,0.9958,0.0039,0.0013</t>
-  </si>
-  <si>
-    <t>0.9962,0.0006,0.0003,0.0015</t>
-  </si>
-  <si>
-    <t>0.0016,0.9974,0.0010,0.0001</t>
-  </si>
-  <si>
-    <t>0.9883,0.0001,0.0001,0.0138</t>
-  </si>
-  <si>
-    <t>0.7177,0.0003,0.0087,0.2182</t>
-  </si>
-  <si>
-    <t>0.9983,0.0003,0.0004,0.0003</t>
-  </si>
-  <si>
-    <t>0.0061,0.0027,0.9820,0.0425</t>
-  </si>
-  <si>
-    <t>0.9803,0.0005,0.0114,0.0006</t>
-  </si>
-  <si>
-    <t>0.9932,0.0010,0.0016,0.0009</t>
-  </si>
-  <si>
-    <t>0.0870,0.7566,0.0905,0.0014</t>
-  </si>
-  <si>
-    <t>0.9599,0.0052,0.0016,0.0054</t>
-  </si>
-  <si>
-    <t>0.9036,0.0147,0.0437,0.0019</t>
-  </si>
-  <si>
-    <t>0.0615,0.8933,0.0453,0.0014</t>
-  </si>
-  <si>
-    <t>0.5800,0.0191,0.3896,0.0004</t>
-  </si>
-  <si>
-    <t>0.4592,0.4208,0.0344,0.0025</t>
-  </si>
-  <si>
-    <t>0.9966,0.0010,0.0002,0.0008</t>
-  </si>
-  <si>
-    <t>0.9964,0.0004,0.0001,0.0018</t>
-  </si>
-  <si>
-    <t>0.9959,0.0008,0.0006,0.0010</t>
-  </si>
-  <si>
-    <t>0.9954,0.0000,0.0001,0.0041</t>
-  </si>
-  <si>
-    <t>0.9948,0.0003,0.0002,0.0026</t>
-  </si>
-  <si>
-    <t>0.9970,0.0005,0.0001,0.0012</t>
-  </si>
-  <si>
-    <t>0.9856,0.0020,0.0007,0.0055</t>
-  </si>
-  <si>
-    <t>0.9975,0.0008,0.0003,0.0003</t>
-  </si>
-  <si>
-    <t>0.0783,0.9118,0.0006,0.0011</t>
-  </si>
-  <si>
-    <t>0.3933,0.6573,0.0036,0.0007</t>
-  </si>
-  <si>
-    <t>0.1747,0.8706,0.0030,0.0001</t>
-  </si>
-  <si>
-    <t>0.0090,0.0603,0.9761,0.0130</t>
-  </si>
-  <si>
-    <t>0.9048,0.1559,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9590,0.0046,0.0033,0.0272</t>
-  </si>
-  <si>
-    <t>0.9783,0.0203,0.0009,0.0003</t>
-  </si>
-  <si>
-    <t>0.1671,0.8560,0.0016,0.0011</t>
-  </si>
-  <si>
-    <t>0.0000,0.0005,1.0000,0.0003</t>
-  </si>
-  <si>
-    <t>0.8935,0.0696,0.0054,0.0183</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0024,0.0790,0.9862,0.0024</t>
-  </si>
-  <si>
-    <t>0.0019,0.0002,0.9971,0.0003</t>
-  </si>
-  <si>
-    <t>0.1209,0.0110,0.8372,0.0017</t>
-  </si>
-  <si>
-    <t>0.0013,0.0009,0.9980,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0020,0.0005,0.9974,0.0001</t>
-  </si>
-  <si>
-    <t>0.0168,0.0044,0.9670,0.0021</t>
-  </si>
-  <si>
-    <t>0.1051,0.0006,0.8781,0.0024</t>
-  </si>
-  <si>
-    <t>0.5412,0.0919,0.1312,0.0108</t>
-  </si>
-  <si>
-    <t>0.5834,0.0028,0.4988,0.0003</t>
-  </si>
-  <si>
-    <t>0.1401,0.0481,0.7824,0.0007</t>
-  </si>
-  <si>
-    <t>0.1687,0.0005,0.8850,0.0001</t>
-  </si>
-  <si>
-    <t>0.8882,0.0023,0.0880,0.0012</t>
-  </si>
-  <si>
-    <t>0.0673,0.0049,0.9037,0.0015</t>
-  </si>
-  <si>
-    <t>0.0091,0.9895,0.0010,0.0004</t>
-  </si>
-  <si>
-    <t>0.0026,0.9971,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.2575,0.8712,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0221,0.9822,0.0006,0.0001</t>
-  </si>
-  <si>
-    <t>0.0215,0.9816,0.0009,0.0001</t>
-  </si>
-  <si>
-    <t>0.7752,0.0468,0.0433,0.0064</t>
-  </si>
-  <si>
-    <t>0.9016,0.0003,0.1139,0.0003</t>
-  </si>
-  <si>
-    <t>0.8987,0.0016,0.0037,0.0201</t>
-  </si>
-  <si>
-    <t>0.7069,0.0295,0.1077,0.0164</t>
-  </si>
-  <si>
-    <t>0.7314,0.0036,0.1884,0.0091</t>
-  </si>
-  <si>
-    <t>0.0062,0.0021,0.9848,0.0063</t>
-  </si>
-  <si>
-    <t>0.1484,0.0674,0.5700,0.0463</t>
-  </si>
-  <si>
-    <t>0.3991,0.0041,0.5472,0.0057</t>
-  </si>
-  <si>
-    <t>0.0212,0.0084,0.9692,0.0002</t>
-  </si>
-  <si>
-    <t>0.1379,0.0974,0.5911,0.0027</t>
-  </si>
-  <si>
-    <t>0.9950,0.0006,0.0000,0.0017</t>
-  </si>
-  <si>
-    <t>0.9755,0.0258,0.0004,0.0006</t>
-  </si>
-  <si>
-    <t>0.9807,0.0156,0.0004,0.0014</t>
-  </si>
-  <si>
-    <t>0.9766,0.0231,0.0008,0.0005</t>
-  </si>
-  <si>
-    <t>0.9568,0.0449,0.0010,0.0011</t>
-  </si>
-  <si>
-    <t>0.9649,0.0366,0.0004,0.0004</t>
-  </si>
-  <si>
-    <t>0.9915,0.0030,0.0002,0.0020</t>
-  </si>
-  <si>
-    <t>0.9940,0.0003,0.0002,0.0048</t>
-  </si>
-  <si>
-    <t>0.0011,0.0009,0.9975,0.0058</t>
-  </si>
-  <si>
-    <t>0.0692,0.0827,0.7993,0.0031</t>
-  </si>
-  <si>
-    <t>0.8067,0.0035,0.1294,0.0094</t>
-  </si>
-  <si>
-    <t>0.0017,0.0000,0.9984,0.0000</t>
-  </si>
-  <si>
-    <t>0.0152,0.0002,0.9812,0.0004</t>
-  </si>
-  <si>
-    <t>0.0258,0.0150,0.9547,0.0007</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0588,0.0033,0.9225,0.0016</t>
+    <t>0.0000,0.0051,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9972,0.8918,0.0000</t>
+  </si>
+  <si>
+    <t>0.9936,0.0035,0.0008,0.0003</t>
+  </si>
+  <si>
+    <t>0.0014,0.9973,0.0012,0.0005</t>
+  </si>
+  <si>
+    <t>0.9955,0.0001,0.0003,0.0026</t>
+  </si>
+  <si>
+    <t>0.0068,0.9915,0.0014,0.0004</t>
+  </si>
+  <si>
+    <t>0.9923,0.0001,0.0003,0.0050</t>
+  </si>
+  <si>
+    <t>0.9226,0.0008,0.0039,0.0396</t>
+  </si>
+  <si>
+    <t>0.9986,0.0004,0.0002,0.0004</t>
+  </si>
+  <si>
+    <t>0.0068,0.0038,0.9807,0.0211</t>
+  </si>
+  <si>
+    <t>0.9756,0.0003,0.0104,0.0029</t>
+  </si>
+  <si>
+    <t>0.9957,0.0003,0.0015,0.0005</t>
+  </si>
+  <si>
+    <t>0.0763,0.8851,0.0231,0.0015</t>
+  </si>
+  <si>
+    <t>0.9540,0.0081,0.0026,0.0025</t>
+  </si>
+  <si>
+    <t>0.8672,0.0276,0.0643,0.0010</t>
+  </si>
+  <si>
+    <t>0.1776,0.2285,0.3923,0.0013</t>
+  </si>
+  <si>
+    <t>0.8759,0.0104,0.0973,0.0004</t>
+  </si>
+  <si>
+    <t>0.7845,0.0469,0.1099,0.0017</t>
+  </si>
+  <si>
+    <t>0.9982,0.0006,0.0000,0.0004</t>
+  </si>
+  <si>
+    <t>0.9986,0.0001,0.0000,0.0012</t>
+  </si>
+  <si>
+    <t>0.9974,0.0003,0.0003,0.0009</t>
+  </si>
+  <si>
+    <t>0.9931,0.0001,0.0002,0.0066</t>
+  </si>
+  <si>
+    <t>0.9976,0.0004,0.0002,0.0006</t>
+  </si>
+  <si>
+    <t>0.9949,0.0017,0.0003,0.0014</t>
+  </si>
+  <si>
+    <t>0.9790,0.0021,0.0008,0.0115</t>
+  </si>
+  <si>
+    <t>0.9961,0.0016,0.0004,0.0003</t>
+  </si>
+  <si>
+    <t>0.0291,0.9591,0.0012,0.0012</t>
+  </si>
+  <si>
+    <t>0.6245,0.3962,0.0036,0.0013</t>
+  </si>
+  <si>
+    <t>0.1911,0.8519,0.0031,0.0003</t>
+  </si>
+  <si>
+    <t>0.0002,0.0680,0.9984,0.0003</t>
+  </si>
+  <si>
+    <t>0.6224,0.5149,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9504,0.0186,0.0037,0.0192</t>
+  </si>
+  <si>
+    <t>0.9780,0.0208,0.0010,0.0002</t>
+  </si>
+  <si>
+    <t>0.0661,0.9166,0.0092,0.0016</t>
+  </si>
+  <si>
+    <t>0.0000,0.0002,1.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9577,0.0182,0.0083,0.0180</t>
   </si>
   <si>
     <t>0.0002,0.0000,0.9998,0.0000</t>
   </si>
   <si>
-    <t>0.0073,0.0001,0.9888,0.0005</t>
-  </si>
-  <si>
-    <t>0.0077,0.0035,0.9835,0.0021</t>
-  </si>
-  <si>
-    <t>0.4179,0.0018,0.5405,0.0048</t>
-  </si>
-  <si>
-    <t>0.8859,0.0001,0.1134,0.0005</t>
-  </si>
-  <si>
-    <t>0.8877,0.0048,0.0083,0.0091</t>
-  </si>
-  <si>
-    <t>0.8870,0.1466,0.0007,0.0003</t>
-  </si>
-  <si>
-    <t>0.9920,0.0075,0.0002,0.0003</t>
-  </si>
-  <si>
-    <t>0.9983,0.0009,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9649,0.0404,0.0005,0.0003</t>
-  </si>
-  <si>
-    <t>0.9064,0.1032,0.0004,0.0008</t>
-  </si>
-  <si>
-    <t>0.9861,0.0196,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9861,0.0144,0.0001,0.0003</t>
-  </si>
-  <si>
-    <t>0.9945,0.0025,0.0001,0.0007</t>
-  </si>
-  <si>
-    <t>0.0102,0.0151,0.9726,0.0003</t>
-  </si>
-  <si>
-    <t>0.0009,0.0001,0.9985,0.0000</t>
-  </si>
-  <si>
-    <t>0.0235,0.0040,0.9638,0.0003</t>
-  </si>
-  <si>
-    <t>0.3959,0.0024,0.6551,0.0004</t>
-  </si>
-  <si>
-    <t>0.0078,0.0000,0.9909,0.0001</t>
-  </si>
-  <si>
-    <t>0.0022,0.0008,0.9624,0.1433</t>
-  </si>
-  <si>
-    <t>0.0238,0.0015,0.9622,0.0015</t>
-  </si>
-  <si>
-    <t>0.0026,0.0000,0.9912,0.0048</t>
-  </si>
-  <si>
-    <t>0.8783,0.0010,0.0012,0.0600</t>
-  </si>
-  <si>
-    <t>0.0000,0.0172,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0007,0.0003,0.0000,0.9998</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.9521,0.0011,0.0052,0.0101</t>
+    <t>0.0056,0.0086,0.9886,0.0002</t>
+  </si>
+  <si>
+    <t>0.0027,0.0005,0.9959,0.0004</t>
+  </si>
+  <si>
+    <t>0.0269,0.0585,0.9319,0.0026</t>
+  </si>
+  <si>
+    <t>0.0010,0.0001,0.9987,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0015,0.0001,0.9980,0.0001</t>
+  </si>
+  <si>
+    <t>0.0164,0.0062,0.9666,0.0024</t>
+  </si>
+  <si>
+    <t>0.0420,0.0022,0.9381,0.0037</t>
+  </si>
+  <si>
+    <t>0.2197,0.1705,0.5504,0.0024</t>
+  </si>
+  <si>
+    <t>0.3429,0.0099,0.6673,0.0008</t>
+  </si>
+  <si>
+    <t>0.0231,0.5017,0.7205,0.0005</t>
+  </si>
+  <si>
+    <t>0.5481,0.0504,0.1659,0.0013</t>
+  </si>
+  <si>
+    <t>0.9480,0.0009,0.0184,0.0009</t>
+  </si>
+  <si>
+    <t>0.2843,0.0131,0.6818,0.0021</t>
+  </si>
+  <si>
+    <t>0.0333,0.9756,0.0005,0.0002</t>
+  </si>
+  <si>
+    <t>0.0028,0.9970,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.0160,0.9897,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.1602,0.8905,0.0007,0.0002</t>
+  </si>
+  <si>
+    <t>0.0351,0.9706,0.0009,0.0001</t>
+  </si>
+  <si>
+    <t>0.0500,0.8683,0.0347,0.0110</t>
+  </si>
+  <si>
+    <t>0.9126,0.0011,0.0655,0.0004</t>
+  </si>
+  <si>
+    <t>0.7323,0.0076,0.0446,0.0623</t>
+  </si>
+  <si>
+    <t>0.4593,0.0027,0.5482,0.0021</t>
+  </si>
+  <si>
+    <t>0.2353,0.0054,0.7439,0.0038</t>
+  </si>
+  <si>
+    <t>0.0141,0.0001,0.9838,0.0006</t>
+  </si>
+  <si>
+    <t>0.0076,0.0099,0.9607,0.0362</t>
+  </si>
+  <si>
+    <t>0.3102,0.0030,0.6844,0.0020</t>
+  </si>
+  <si>
+    <t>0.1241,0.0104,0.8362,0.0016</t>
+  </si>
+  <si>
+    <t>0.0574,0.0433,0.8580,0.0039</t>
+  </si>
+  <si>
+    <t>0.9921,0.0020,0.0001,0.0022</t>
+  </si>
+  <si>
+    <t>0.9932,0.0044,0.0004,0.0008</t>
+  </si>
+  <si>
+    <t>0.9878,0.0031,0.0001,0.0026</t>
+  </si>
+  <si>
+    <t>0.9670,0.0375,0.0005,0.0004</t>
+  </si>
+  <si>
+    <t>0.9451,0.0549,0.0025,0.0010</t>
+  </si>
+  <si>
+    <t>0.9884,0.0105,0.0002,0.0004</t>
+  </si>
+  <si>
+    <t>0.9935,0.0009,0.0001,0.0026</t>
+  </si>
+  <si>
+    <t>0.9921,0.0001,0.0001,0.0083</t>
+  </si>
+  <si>
+    <t>0.0009,0.0034,0.9970,0.0092</t>
+  </si>
+  <si>
+    <t>0.0631,0.7532,0.1869,0.0044</t>
+  </si>
+  <si>
+    <t>0.6039,0.0065,0.2442,0.0451</t>
+  </si>
+  <si>
+    <t>0.0057,0.0000,0.9950,0.0000</t>
+  </si>
+  <si>
+    <t>0.0065,0.0005,0.9922,0.0002</t>
+  </si>
+  <si>
+    <t>0.0865,0.0305,0.8613,0.0010</t>
+  </si>
+  <si>
+    <t>0.0015,0.0001,0.9982,0.0000</t>
+  </si>
+  <si>
+    <t>0.1527,0.0029,0.8218,0.0028</t>
+  </si>
+  <si>
+    <t>0.0009,0.0000,0.9992,0.0000</t>
+  </si>
+  <si>
+    <t>0.2694,0.0001,0.7570,0.0002</t>
+  </si>
+  <si>
+    <t>0.0138,0.0148,0.9691,0.0005</t>
+  </si>
+  <si>
+    <t>0.4760,0.0083,0.4245,0.0125</t>
+  </si>
+  <si>
+    <t>0.9728,0.0001,0.0095,0.0002</t>
+  </si>
+  <si>
+    <t>0.9655,0.0004,0.0029,0.0021</t>
+  </si>
+  <si>
+    <t>0.7330,0.3347,0.0007,0.0003</t>
+  </si>
+  <si>
+    <t>0.9954,0.0039,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9983,0.0008,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9555,0.0580,0.0004,0.0002</t>
+  </si>
+  <si>
+    <t>0.9461,0.0476,0.0010,0.0019</t>
+  </si>
+  <si>
+    <t>0.9863,0.0185,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9823,0.0182,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.9821,0.0133,0.0005,0.0012</t>
+  </si>
+  <si>
+    <t>0.0197,0.0008,0.9771,0.0001</t>
+  </si>
+  <si>
+    <t>0.0014,0.0003,0.9973,0.0001</t>
+  </si>
+  <si>
+    <t>0.0031,0.0017,0.9931,0.0002</t>
+  </si>
+  <si>
+    <t>0.4251,0.0017,0.6351,0.0005</t>
+  </si>
+  <si>
+    <t>0.0033,0.0000,0.9956,0.0001</t>
+  </si>
+  <si>
+    <t>0.0214,0.0010,0.7515,0.2767</t>
+  </si>
+  <si>
+    <t>0.1093,0.0003,0.8649,0.0021</t>
+  </si>
+  <si>
+    <t>0.0280,0.0003,0.9559,0.0030</t>
+  </si>
+  <si>
+    <t>0.5982,0.0009,0.0003,0.4162</t>
+  </si>
+  <si>
+    <t>0.0000,0.3335,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.0015,0.0002,0.0000,0.9996</t>
+  </si>
+  <si>
+    <t>0.8541,0.0023,0.0004,0.0508</t>
   </si>
 </sst>
 </file>
@@ -1950,7 +1959,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1964,7 +1973,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1978,7 +1987,7 @@
         <v>260</v>
       </c>
       <c r="D4" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1992,7 +2001,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2006,7 +2015,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2020,7 +2029,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2034,7 +2043,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2048,7 +2057,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2062,7 +2071,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2076,7 +2085,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2090,7 +2099,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2104,7 +2113,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2115,10 +2124,10 @@
         <v>259</v>
       </c>
       <c r="C14" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D14" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2132,7 +2141,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2143,10 +2152,10 @@
         <v>261</v>
       </c>
       <c r="C16" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D16" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2160,7 +2169,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2171,10 +2180,10 @@
         <v>259</v>
       </c>
       <c r="C18" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2188,7 +2197,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2202,7 +2211,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2216,7 +2225,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2230,7 +2239,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2244,7 +2253,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2255,10 +2264,10 @@
         <v>259</v>
       </c>
       <c r="C24" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D24" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2269,10 +2278,10 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D25" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2286,7 +2295,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2300,7 +2309,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2314,7 +2323,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2325,10 +2334,10 @@
         <v>261</v>
       </c>
       <c r="C29" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D29" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2342,7 +2351,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2356,7 +2365,7 @@
         <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2370,7 +2379,7 @@
         <v>261</v>
       </c>
       <c r="D32" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2384,7 +2393,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2398,7 +2407,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2409,10 +2418,10 @@
         <v>259</v>
       </c>
       <c r="C35" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2426,7 +2435,7 @@
         <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2440,7 +2449,7 @@
         <v>262</v>
       </c>
       <c r="D37" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2454,7 +2463,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2468,7 +2477,7 @@
         <v>262</v>
       </c>
       <c r="D39" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2482,7 +2491,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2496,7 +2505,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2510,7 +2519,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2524,7 +2533,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2538,7 +2547,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2552,7 +2561,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2563,10 +2572,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D46" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2580,7 +2589,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2594,7 +2603,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2608,7 +2617,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2622,7 +2631,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2633,10 +2642,10 @@
         <v>261</v>
       </c>
       <c r="C51" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2650,7 +2659,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2664,7 +2673,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2678,7 +2687,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2692,7 +2701,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2706,7 +2715,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2720,7 +2729,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2734,7 +2743,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2748,7 +2757,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2762,7 +2771,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2776,7 +2785,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2790,7 +2799,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2804,7 +2813,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2818,7 +2827,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2832,7 +2841,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2846,7 +2855,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2860,7 +2869,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2874,7 +2883,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2888,7 +2897,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2899,10 +2908,10 @@
         <v>259</v>
       </c>
       <c r="C70" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D70" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2913,10 +2922,10 @@
         <v>261</v>
       </c>
       <c r="C71" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2930,7 +2939,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2944,7 +2953,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2958,7 +2967,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2972,7 +2981,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2983,10 +2992,10 @@
         <v>262</v>
       </c>
       <c r="C76" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3000,7 +3009,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3014,7 +3023,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3028,7 +3037,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3042,7 +3051,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3056,7 +3065,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3070,7 +3079,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3084,7 +3093,7 @@
         <v>262</v>
       </c>
       <c r="D83" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3098,7 +3107,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3112,7 +3121,7 @@
         <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3126,7 +3135,7 @@
         <v>263</v>
       </c>
       <c r="D86" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3140,7 +3149,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3151,10 +3160,10 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3168,7 +3177,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>269</v>
+        <v>354</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3182,7 +3191,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3196,7 +3205,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3210,7 +3219,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3224,7 +3233,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3238,7 +3247,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3252,7 +3261,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3266,7 +3275,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3280,7 +3289,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3294,7 +3303,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3308,7 +3317,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3322,7 +3331,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3336,7 +3345,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3350,7 +3359,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3364,7 +3373,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3378,7 +3387,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3392,7 +3401,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3406,7 +3415,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3420,7 +3429,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3434,7 +3443,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3448,7 +3457,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3462,7 +3471,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3476,7 +3485,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3490,7 +3499,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3504,7 +3513,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3518,7 +3527,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>332</v>
+        <v>379</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3532,7 +3541,7 @@
         <v>262</v>
       </c>
       <c r="D115" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3543,10 +3552,10 @@
         <v>259</v>
       </c>
       <c r="C116" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D116" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3557,10 +3566,10 @@
         <v>261</v>
       </c>
       <c r="C117" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D117" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3574,7 +3583,7 @@
         <v>259</v>
       </c>
       <c r="D118" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3585,10 +3594,10 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D119" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3602,7 +3611,7 @@
         <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3616,7 +3625,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3630,7 +3639,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3644,7 +3653,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3658,7 +3667,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3672,7 +3681,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3686,7 +3695,7 @@
         <v>262</v>
       </c>
       <c r="D126" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3700,7 +3709,7 @@
         <v>262</v>
       </c>
       <c r="D127" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3714,7 +3723,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3728,7 +3737,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3742,7 +3751,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3756,7 +3765,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3770,7 +3779,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3784,7 +3793,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3798,7 +3807,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3812,7 +3821,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3826,7 +3835,7 @@
         <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3837,10 +3846,10 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D137" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3854,7 +3863,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3868,7 +3877,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3882,7 +3891,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3896,7 +3905,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3910,7 +3919,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3924,7 +3933,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3938,7 +3947,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3952,7 +3961,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3966,7 +3975,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3980,7 +3989,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3994,7 +4003,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4008,7 +4017,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4022,7 +4031,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4036,7 +4045,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4050,7 +4059,7 @@
         <v>262</v>
       </c>
       <c r="D152" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4064,7 +4073,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4078,7 +4087,7 @@
         <v>259</v>
       </c>
       <c r="D154" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4092,7 +4101,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4106,7 +4115,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4120,7 +4129,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4134,7 +4143,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4148,7 +4157,7 @@
         <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4162,7 +4171,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4176,7 +4185,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4187,10 +4196,10 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D162" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4204,7 +4213,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4218,7 +4227,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4232,7 +4241,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4246,7 +4255,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4260,7 +4269,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4274,7 +4283,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4288,7 +4297,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4302,7 +4311,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4316,7 +4325,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4330,7 +4339,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4344,7 +4353,7 @@
         <v>262</v>
       </c>
       <c r="D173" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4355,10 +4364,10 @@
         <v>259</v>
       </c>
       <c r="C174" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4372,7 +4381,7 @@
         <v>262</v>
       </c>
       <c r="D175" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4386,7 +4395,7 @@
         <v>261</v>
       </c>
       <c r="D176" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4397,10 +4406,10 @@
         <v>259</v>
       </c>
       <c r="C177" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="D177" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4414,7 +4423,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4428,7 +4437,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4442,7 +4451,7 @@
         <v>262</v>
       </c>
       <c r="D180" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4456,7 +4465,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4470,7 +4479,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4484,7 +4493,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4498,7 +4507,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4512,7 +4521,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4526,7 +4535,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4540,7 +4549,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4554,7 +4563,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4568,7 +4577,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4582,7 +4591,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4596,7 +4605,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4607,10 +4616,10 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D192" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4621,10 +4630,10 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D193" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4635,10 +4644,10 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D194" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4649,10 +4658,10 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D195" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4666,7 +4675,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4680,7 +4689,7 @@
         <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4694,7 +4703,7 @@
         <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4708,7 +4717,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4722,7 +4731,7 @@
         <v>262</v>
       </c>
       <c r="D200" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4736,7 +4745,7 @@
         <v>262</v>
       </c>
       <c r="D201" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4750,7 +4759,7 @@
         <v>262</v>
       </c>
       <c r="D202" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4761,10 +4770,10 @@
         <v>259</v>
       </c>
       <c r="C203" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D203" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4778,7 +4787,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4792,7 +4801,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4803,10 +4812,10 @@
         <v>261</v>
       </c>
       <c r="C206" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D206" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4817,10 +4826,10 @@
         <v>259</v>
       </c>
       <c r="C207" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D207" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4834,7 +4843,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4848,7 +4857,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4862,7 +4871,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4876,7 +4885,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4890,7 +4899,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4904,7 +4913,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4918,7 +4927,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4932,7 +4941,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4946,7 +4955,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4960,7 +4969,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4974,7 +4983,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4988,7 +4997,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5002,7 +5011,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5016,7 +5025,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5027,10 +5036,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D222" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5044,7 +5053,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5058,7 +5067,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5072,7 +5081,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5086,7 +5095,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5100,7 +5109,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5114,7 +5123,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5128,7 +5137,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5142,7 +5151,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5156,7 +5165,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5167,10 +5176,10 @@
         <v>259</v>
       </c>
       <c r="C232" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D232" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5184,7 +5193,7 @@
         <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5198,7 +5207,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5212,7 +5221,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5226,7 +5235,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5240,7 +5249,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5254,7 +5263,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5268,7 +5277,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>500</v>
+        <v>504</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5282,7 +5291,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5296,7 +5305,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5310,7 +5319,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5324,7 +5333,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5338,7 +5347,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>505</v>
+        <v>509</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5352,7 +5361,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>506</v>
+        <v>510</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5366,7 +5375,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>507</v>
+        <v>511</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5380,7 +5389,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>508</v>
+        <v>512</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5394,7 +5403,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>509</v>
+        <v>513</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5408,7 +5417,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5422,7 +5431,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5436,7 +5445,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>512</v>
+        <v>516</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5450,7 +5459,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>513</v>
+        <v>517</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5464,7 +5473,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>514</v>
+        <v>518</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5478,7 +5487,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>515</v>
+        <v>343</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5492,7 +5501,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>515</v>
+        <v>343</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5506,7 +5515,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
     </row>
   </sheetData>
